--- a/Documentos/Documentos Excel - Hojas de calculo/Comercio de informática.xlsx
+++ b/Documentos/Documentos Excel - Hojas de calculo/Comercio de informática.xlsx
@@ -384,19 +384,19 @@
     <t>6-Los bordes de la tabla del total general y total de la columna total neto.</t>
   </si>
   <si>
-    <t>7-Alinear el texto.</t>
-  </si>
-  <si>
-    <t>8-El formato moneda sin espacios y el porcentaje.</t>
-  </si>
-  <si>
-    <t>1-Combinar celdas en el titulo.</t>
-  </si>
-  <si>
     <t>2-Los colores correspondientes con el balde de pintura.</t>
   </si>
   <si>
     <t>Comercio de informática</t>
+  </si>
+  <si>
+    <t>1-Centrar y combinar celdas en el titulo.</t>
+  </si>
+  <si>
+    <t>7-Alineacion del texto, en izquierda, centro y derecha como su muestra en la tabla.</t>
+  </si>
+  <si>
+    <t>8-El formato moneda y el porcentaje.</t>
   </si>
 </sst>
 </file>
@@ -918,7 +918,7 @@
   <sheetData>
     <row r="1" spans="1:14">
       <c r="A1" s="21" t="s">
-        <v>125</v>
+        <v>122</v>
       </c>
       <c r="B1" s="21"/>
       <c r="C1" s="21"/>
@@ -2195,7 +2195,7 @@
     </row>
     <row r="37" spans="1:3">
       <c r="B37" t="s">
-        <v>124</v>
+        <v>121</v>
       </c>
     </row>
     <row r="38" spans="1:3">
@@ -2225,14 +2225,14 @@
     <row r="42" spans="1:3">
       <c r="A42" s="17"/>
       <c r="B42" s="17" t="s">
-        <v>121</v>
+        <v>124</v>
       </c>
       <c r="C42" s="17"/>
     </row>
     <row r="43" spans="1:3">
       <c r="A43" s="17"/>
       <c r="B43" s="17" t="s">
-        <v>122</v>
+        <v>125</v>
       </c>
       <c r="C43" s="17"/>
     </row>
